--- a/naver-place-crawler/results_health/인천_PT.xlsx
+++ b/naver-place-crawler/results_health/인천_PT.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>청라재활PT 피지오쏭운동센터</t>
+          <t>카우짐24시 서구청역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>l2037002@naver.com</t>
+          <t>coco951215@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1399-9872</t>
+          <t>0507-1376-7926</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 서구 청라커낼로260번길 11 1동 10층 1010호</t>
+          <t>인천 서구 탁옥로51번길 11 702호, 703호, 704호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/l2037002</t>
+          <t>https://link.inpock.co.kr/cowgymseogu</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4glgw</t>
+          <t>https://talk.naver.com/ct/w5xn31</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -621,17 +621,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>138</v>
+        <v>1021</v>
       </c>
       <c r="Q2" t="n">
-        <v>285</v>
+        <v>324</v>
       </c>
       <c r="R2" t="n">
-        <v>423</v>
+        <v>1345</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1128948740</t>
+          <t>1106839652</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1128948740</t>
+          <t>https://m.place.naver.com/place/1106839652</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,49 +657,49 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>바름핏 PT&amp;필라테스 본점</t>
+          <t>무포스 PT FT 송도점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>brfpt@naver.com</t>
+          <t>moveforstrength@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1455-8691</t>
+          <t>0507-1406-4500</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천 미추홀구 소성로 150 2층바름핏</t>
+          <t>인천 연수구 인천타워대로197번길 16 2층 226호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bareumfit</t>
+          <t>https://www.moveforstrength.co.kr/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4yrsh</t>
+          <t>https://talk.naver.com/ct/w5x24z</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>287</v>
+        <v>115</v>
       </c>
       <c r="Q3" t="n">
-        <v>375</v>
+        <v>644</v>
       </c>
       <c r="R3" t="n">
-        <v>662</v>
+        <v>759</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1493566392</t>
+          <t>1426191152</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1493566392</t>
+          <t>https://m.place.naver.com/place/1426191152</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>여성전용PT복숭아헬스장</t>
+          <t>커넥트짐 구월동 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>52997994@naver.com</t>
+          <t>connectgympro@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1417-8063</t>
+          <t>0507-1382-1877</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천 남동구 인주대로 588 대암빌딩 2층</t>
+          <t>인천 남동구 인주대로 593 엔타스빌딩 1층 커넥트짐 구월점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://youtube.com//@복숭아헬스장</t>
+          <t>https://www.instagram.com/connectgym.pro</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wit7sbd</t>
+          <t>https://talk.naver.com/ct/wz5kx6y</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>125</v>
+        <v>656</v>
       </c>
       <c r="Q4" t="n">
-        <v>322</v>
+        <v>872</v>
       </c>
       <c r="R4" t="n">
-        <v>447</v>
+        <v>1528</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2040870567</t>
+          <t>1964930363</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040870567</t>
+          <t>https://m.place.naver.com/place/1964930363</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>커넥트짐 구월동 헬스&amp;PT</t>
+          <t>샤머니짐 송도점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>connectgympro@naver.com</t>
+          <t>shamanigym_songdo@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1382-1877</t>
+          <t>0507-1330-9030</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천 남동구 인주대로 593 엔타스빌딩 1층 커넥트짐 구월점</t>
+          <t>인천 연수구 컨벤시아대로 81 드림시티 7층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/connectgym.pro</t>
+          <t>https://www.instagram.com/shamanigym/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wz5kx6y</t>
+          <t>https://talk.naver.com/ct/w7ng6u3</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>656</v>
+        <v>1386</v>
       </c>
       <c r="Q5" t="n">
-        <v>869</v>
+        <v>933</v>
       </c>
       <c r="R5" t="n">
-        <v>1525</v>
+        <v>2319</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1964930363</t>
+          <t>1040543457</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1964930363</t>
+          <t>https://m.place.naver.com/place/1040543457</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,34 +956,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>샤머니짐 송도점</t>
+          <t>더피티짐 프리미엄 학원가점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>shamanigym_songdo@naver.com</t>
+          <t>qoqofh677@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1330-9030</t>
+          <t>0507-1446-9681</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천 연수구 컨벤시아대로 81 드림시티 7층</t>
+          <t>인천 연수구 해돋이로 160-19 카리스프라자 3층 301��</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shamanigym/</t>
+          <t>https://theptgym.clickn.co.kr/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w7ng6u3</t>
+          <t>https://talk.naver.com/ct/w4mk22</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1386</v>
+        <v>317</v>
       </c>
       <c r="Q6" t="n">
-        <v>933</v>
+        <v>1924</v>
       </c>
       <c r="R6" t="n">
-        <v>2319</v>
+        <v>2241</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1040543457</t>
+          <t>1063156519</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040543457</t>
+          <t>https://m.place.naver.com/place/1063156519</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">

--- a/naver-place-crawler/results_health/인천_PT.xlsx
+++ b/naver-place-crawler/results_health/인천_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 서구 탁옥로51번길 11 702호, 703호, 704호</t>
+          <t>인천광역시 서구 탁옥로51번길 11 702호, 703호, 704호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5xn31</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -662,39 +658,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>무포스 PT FT 송도점</t>
+          <t>아이언휘트니스 헬스&amp;PT 삼산점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>moveforstrength@naver.com</t>
+          <t>ironfitnesssamsan@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1406-4500</t>
+          <t>0507-1483-2126</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천 연수구 인천타워대로197번길 16 2층 226호</t>
+          <t>인천광역시 부평구 부평북로 448 로얄프라자 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.moveforstrength.co.kr/</t>
+          <t>https://blog.naver.com/ironfitnesssamsan</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -704,17 +700,13 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5x24z</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>115</v>
+        <v>710</v>
       </c>
       <c r="Q3" t="n">
-        <v>644</v>
+        <v>291</v>
       </c>
       <c r="R3" t="n">
-        <v>759</v>
+        <v>1001</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1426191152</t>
+          <t>1098353648</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1426191152</t>
+          <t>https://m.place.naver.com/place/1098353648</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -777,7 +769,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천 남동구 인주대로 593 엔타스빌딩 1층 커넥트짐 구월점</t>
+          <t>인천광역시 남동구 인주대로 593 엔타스빌딩 1층 커넥트짐 구월점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wz5kx6y</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>O</t>
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="Q4" t="n">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="R4" t="n">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -875,7 +863,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천 연수구 컨벤시아대로 81 드림시티 7층</t>
+          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7ng6u3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -973,7 +957,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 160-19 카리스프라자 3층 301��</t>
+          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -998,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4mk22</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1020,10 +1000,10 @@
         <v>317</v>
       </c>
       <c r="Q6" t="n">
-        <v>1924</v>
+        <v>1928</v>
       </c>
       <c r="R6" t="n">
-        <v>2241</v>
+        <v>2245</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1047,25 +1027,41 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>무포스 PT FT 송도점</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>moveforstrength@naver.com</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1406-4500</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>인천광역시 연수구 인천타워대로197번길 16 2층 226호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.moveforstrength.co.kr/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1075,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,17 +1087,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>644</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>759</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>7043481</t>
+          <t>1426191152</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7043481</t>
+          <t>https://m.place.naver.com/place/1426191152</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1188,12 +1184,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>7279520</t>
+          <t>7043481</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7279520</t>
+          <t>https://m.place.naver.com/place/7043481</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1266,12 +1262,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7166733</t>
+          <t>7279520</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7166733</t>
+          <t>https://m.place.naver.com/place/7279520</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1344,12 +1340,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>7226084</t>
+          <t>7166733</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7226084</t>
+          <t>https://m.place.naver.com/place/7166733</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1422,15 +1418,93 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>7226084</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7226084</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>7484708</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/7484708</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/인천_PT.xlsx
+++ b/naver-place-crawler/results_health/인천_PT.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 서구 탁옥로51번길 11 702호, 703호, 704호</t>
+          <t>인천 서구 탁옥로51번길 11 702호, 703호, 704호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5xn31</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="Q2" t="n">
         <v>324</v>
       </c>
       <c r="R2" t="n">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -653,39 +657,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>아이언휘트니스 헬스&amp;PT 삼산점</t>
+          <t>더피티짐 프리미엄 학원가점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ironfitnesssamsan@naver.com</t>
+          <t>qoqofh677@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1483-2126</t>
+          <t>0507-1446-9681</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부평북로 448 로얄프라자 2층</t>
+          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ironfitnesssamsan</t>
+          <t>https://theptgym.clickn.co.kr/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -706,7 +710,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>710</v>
+        <v>317</v>
       </c>
       <c r="Q3" t="n">
-        <v>291</v>
+        <v>1930</v>
       </c>
       <c r="R3" t="n">
-        <v>1001</v>
+        <v>2247</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1098353648</t>
+          <t>1063156519</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1098353648</t>
+          <t>https://m.place.naver.com/place/1063156519</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="Q4" t="n">
         <v>870</v>
       </c>
       <c r="R4" t="n">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -903,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="Q5" t="n">
         <v>933</v>
       </c>
       <c r="R5" t="n">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -940,34 +944,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>더피티짐 프리미엄 학원가점</t>
+          <t>여성전용PT복숭아헬스장</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>qoqofh677@naver.com</t>
+          <t>52997994@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1446-9681</t>
+          <t>0507-1417-8063</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
+          <t>인천광역시 남동구 인주대로 588 대암빌딩 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://theptgym.clickn.co.kr/</t>
+          <t>https://youtube.com//@복숭아헬스장</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -997,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>317</v>
+        <v>125</v>
       </c>
       <c r="Q6" t="n">
-        <v>1928</v>
+        <v>337</v>
       </c>
       <c r="R6" t="n">
-        <v>2245</v>
+        <v>462</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1063156519</t>
+          <t>2040870567</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1063156519</t>
+          <t>https://m.place.naver.com/place/2040870567</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>무포스 PT FT 송도점</t>
+          <t>피트니스 연구소 부평산곡점 헬스PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>moveforstrength@naver.com</t>
+          <t>lfitness5@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1406-4500</t>
+          <t>0507-1349-2251</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로197번길 16 2층 226호</t>
+          <t>인천광역시 부평구 원적로 295 더 루츠 스퀘어 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.moveforstrength.co.kr/</t>
+          <t>http://fitnessinstitute.co.kr/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,7 +1070,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1082,7 +1086,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>115</v>
+        <v>986</v>
       </c>
       <c r="Q7" t="n">
-        <v>644</v>
+        <v>492</v>
       </c>
       <c r="R7" t="n">
-        <v>759</v>
+        <v>1478</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1426191152</t>
+          <t>1338376061</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1426191152</t>
+          <t>https://m.place.naver.com/place/1338376061</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1121,35 +1125,51 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>피트니스 연구소 송도점 헬스PT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>fitnessinssongdo@naver.com</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1468-2286</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>인천광역시 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://fitnessinstitute.co.kr/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1160,22 +1180,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1578</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>731</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2309</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1184,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>7043481</t>
+          <t>1806077033</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7043481</t>
+          <t>https://m.place.naver.com/place/1806077033</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1262,12 +1282,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7279520</t>
+          <t>7043481</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7279520</t>
+          <t>https://m.place.naver.com/place/7043481</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1340,12 +1360,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>7166733</t>
+          <t>7279520</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7166733</t>
+          <t>https://m.place.naver.com/place/7279520</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1418,12 +1438,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>7226084</t>
+          <t>7166733</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7226084</t>
+          <t>https://m.place.naver.com/place/7166733</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1496,15 +1516,93 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
+          <t>7226084</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7226084</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>7484708</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/7484708</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/인천_PT.xlsx
+++ b/naver-place-crawler/results_health/인천_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,49 +559,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>카우짐24시 서구청역점</t>
+          <t>청라재활PT 피지오쏭운동센터</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>coco951215@naver.com</t>
+          <t>l2037002@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1376-7926</t>
+          <t>0507-1399-9872</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 서구 탁옥로51번길 11 702호, 703호, 704호</t>
+          <t>인천 서구 청라커낼로260번길 11 1동 10층 1010호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/cowgymseogu</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5xn31</t>
+          <t>https://talk.naver.com/ct/w4glgw</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -621,17 +621,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1020</v>
+        <v>138</v>
       </c>
       <c r="Q2" t="n">
-        <v>324</v>
+        <v>285</v>
       </c>
       <c r="R2" t="n">
-        <v>1344</v>
+        <v>423</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,51 +640,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1106839652</t>
+          <t>1128948740</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1106839652</t>
+          <t>https://m.place.naver.com/place/1128948740</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>더피티짐 프리미엄 학원가점</t>
+          <t>카우짐24시 서구청역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>qoqofh677@naver.com</t>
+          <t>cowgym_@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1446-9681</t>
+          <t>0507-1376-7926</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
+          <t>인천 서구 탁옥로51번길 11 702호, 703호, 704호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://theptgym.clickn.co.kr/</t>
+          <t>https://link.inpock.co.kr/cowgymseogu</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,15 +699,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5xn31</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,17 +719,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>317</v>
+        <v>1020</v>
       </c>
       <c r="Q3" t="n">
-        <v>1930</v>
+        <v>324</v>
       </c>
       <c r="R3" t="n">
-        <v>2247</v>
+        <v>1344</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1063156519</t>
+          <t>1106839652</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1063156519</t>
+          <t>https://m.place.naver.com/place/1106839652</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -756,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>커넥트짐 구월동 헬스&amp;PT</t>
+          <t>여성전용PT복숭아헬스장</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>connectgympro@naver.com</t>
+          <t>52997994@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1382-1877</t>
+          <t>0507-1417-8063</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인주대로 593 엔타스빌딩 1층 커넥트짐 구월점</t>
+          <t>인천 남동구 인주대로 588 대암빌딩 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/connectgym.pro</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -798,13 +802,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wit7sbd</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>658</v>
+        <v>125</v>
       </c>
       <c r="Q4" t="n">
-        <v>870</v>
+        <v>352</v>
       </c>
       <c r="R4" t="n">
-        <v>1528</v>
+        <v>477</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1964930363</t>
+          <t>2040870567</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1964930363</t>
+          <t>https://m.place.naver.com/place/2040870567</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -850,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>샤머니짐 송도점</t>
+          <t>커넥트짐 구월동 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>shamanigym_songdo@naver.com</t>
+          <t>connectgympro@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1330-9030</t>
+          <t>0507-1382-1877</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
+          <t>인천 남동구 인주대로 593 엔타스빌딩 1층 커넥트짐 구월점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shamanigym/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -882,7 +890,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -892,13 +900,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wz5kx6y</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -907,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1387</v>
+        <v>658</v>
       </c>
       <c r="Q5" t="n">
-        <v>933</v>
+        <v>870</v>
       </c>
       <c r="R5" t="n">
-        <v>2320</v>
+        <v>1528</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1040543457</t>
+          <t>1964930363</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040543457</t>
+          <t>https://m.place.naver.com/place/1964930363</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -944,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>여성전용PT복숭아헬스장</t>
+          <t>샤머니짐 송도점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>52997994@naver.com</t>
+          <t>resort_6@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1417-8063</t>
+          <t>0507-1330-9030</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인주대로 588 대암빌딩 2층</t>
+          <t>인천 연수구 컨벤시아대로 81 드림시티 7층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://youtube.com//@복숭아헬스장</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -976,7 +988,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -986,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7ng6u3</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1001,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>125</v>
+        <v>1387</v>
       </c>
       <c r="Q6" t="n">
-        <v>337</v>
+        <v>933</v>
       </c>
       <c r="R6" t="n">
-        <v>462</v>
+        <v>2320</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,51 +1032,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2040870567</t>
+          <t>1040543457</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040870567</t>
+          <t>https://m.place.naver.com/place/1040543457</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피트니스 연구소 부평산곡점 헬스PT</t>
+          <t>더피티짐 프리미엄 학원가점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lfitness5@naver.com</t>
+          <t>qoqofh677@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1349-2251</t>
+          <t>0507-1446-9681</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 원적로 295 더 루츠 스퀘어 5층</t>
+          <t>인천 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://fitnessinstitute.co.kr/</t>
+          <t>https://theptgym.clickn.co.kr/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1075,18 +1091,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4mk22</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1095,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>986</v>
+        <v>317</v>
       </c>
       <c r="Q7" t="n">
-        <v>492</v>
+        <v>1930</v>
       </c>
       <c r="R7" t="n">
-        <v>1478</v>
+        <v>2247</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,66 +1130,50 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1338376061</t>
+          <t>1063156519</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1338376061</t>
+          <t>https://m.place.naver.com/place/1063156519</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>피트니스 연구소 송도점 헬스PT</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>fitnessinssongdo@naver.com</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1468-2286</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://fitnessinstitute.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1180,22 +1184,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1578</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>731</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2309</v>
+        <v>0</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,17 +1208,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1806077033</t>
+          <t>7043481</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806077033</t>
+          <t>https://m.place.naver.com/place/7043481</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1282,17 +1286,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7043481</t>
+          <t>7279520</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7043481</t>
+          <t>https://m.place.naver.com/place/7279520</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1360,17 +1364,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>7279520</t>
+          <t>7166733</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7279520</t>
+          <t>https://m.place.naver.com/place/7166733</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1438,17 +1442,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>7166733</t>
+          <t>7226084</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7166733</t>
+          <t>https://m.place.naver.com/place/7226084</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1516,95 +1520,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>7226084</t>
+          <t>7484708</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7226084</t>
+          <t>https://m.place.naver.com/place/7484708</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>7484708</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/7484708</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/인천_PT.xlsx
+++ b/naver-place-crawler/results_health/인천_PT.xlsx
@@ -421,18 +421,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,61 +559,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>청라재활PT 피지오쏭운동센터</t>
+          <t>카우짐24시 서구청역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>l2037002@naver.com</t>
+          <t>coco951215@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1399-9872</t>
+          <t>0507-1376-7926</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 서구 청라커낼로260번길 11 1동 10층 1010호</t>
+          <t>인천광역시 서구 탁옥로51번길 11 702호, 703호, 704호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://link.inpock.co.kr/cowgymseogu</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4glgw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>138</v>
+        <v>1020</v>
       </c>
       <c r="Q2" t="n">
-        <v>285</v>
+        <v>324</v>
       </c>
       <c r="R2" t="n">
-        <v>423</v>
+        <v>1344</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1128948740</t>
+          <t>1106839652</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1128948740</t>
+          <t>https://m.place.naver.com/place/1106839652</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>카우짐24시 서구청역점</t>
+          <t>아이언휘트니스 헬스&amp;PT 삼산점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cowgym_@naver.com</t>
+          <t>ironfitnesssamsan@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1376-7926</t>
+          <t>0507-1483-2126</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천 서구 탁옥로51번길 11 702호, 703호, 704호</t>
+          <t>인천광역시 부평구 부평북로 448 로얄프라자 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/cowgymseogu</t>
+          <t>https://blog.naver.com/ironfitnesssamsan</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -704,32 +700,28 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5xn31</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1020</v>
+        <v>710</v>
       </c>
       <c r="Q3" t="n">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="R3" t="n">
-        <v>1344</v>
+        <v>1001</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1106839652</t>
+          <t>1098353648</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1106839652</t>
+          <t>https://m.place.naver.com/place/1098353648</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>여성전용PT복숭아헬스장</t>
+          <t>커넥트짐 구월동 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>52997994@naver.com</t>
+          <t>connectgympro@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1417-8063</t>
+          <t>0507-1382-1877</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천 남동구 인주대로 588 대암빌딩 2층</t>
+          <t>인천광역시 남동구 인주대로 593 엔타스빌딩 1층 커넥트짐 구월점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/connectgym.pro</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +784,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -802,17 +794,13 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wit7sbd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>125</v>
+        <v>658</v>
       </c>
       <c r="Q4" t="n">
-        <v>352</v>
+        <v>870</v>
       </c>
       <c r="R4" t="n">
-        <v>477</v>
+        <v>1528</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2040870567</t>
+          <t>1964930363</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040870567</t>
+          <t>https://m.place.naver.com/place/1964930363</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>커넥트짐 구월동 헬스&amp;PT</t>
+          <t>샤머니짐 송도점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>connectgympro@naver.com</t>
+          <t>shamanigym_songdo@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1382-1877</t>
+          <t>0507-1330-9030</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천 남동구 인주대로 593 엔타스빌딩 1층 커넥트짐 구월점</t>
+          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/shamanigym/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,7 +878,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -900,17 +888,13 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wz5kx6y</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>658</v>
+        <v>1387</v>
       </c>
       <c r="Q5" t="n">
-        <v>870</v>
+        <v>933</v>
       </c>
       <c r="R5" t="n">
-        <v>1528</v>
+        <v>2320</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1964930363</t>
+          <t>1040543457</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1964930363</t>
+          <t>https://m.place.naver.com/place/1040543457</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,39 +940,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>샤머니짐 송도점</t>
+          <t>더피티짐 프리미엄 학원가점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>resort_6@naver.com</t>
+          <t>qoqofh677@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1330-9030</t>
+          <t>0507-1446-9681</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천 연수구 컨벤시아대로 81 드림시티 7층</t>
+          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://theptgym.clickn.co.kr/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -998,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7ng6u3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1017,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1387</v>
+        <v>317</v>
       </c>
       <c r="Q6" t="n">
-        <v>933</v>
+        <v>1932</v>
       </c>
       <c r="R6" t="n">
-        <v>2320</v>
+        <v>2249</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1040543457</t>
+          <t>1063156519</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040543457</t>
+          <t>https://m.place.naver.com/place/1063156519</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,34 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>더피티짐 프리미엄 학원가점</t>
+          <t>더피티짐 프리미엄 루원시티점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>qoqofh677@naver.com</t>
+          <t>gktk1877@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1446-9681</t>
+          <t>0507-1375-9681</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
+          <t>인천광역시 서구 봉오대로 270 302동 상가B 110~112호 (파리바게트 위층)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://theptgym.clickn.co.kr/</t>
+          <t>https://blog.naver.com/gktk1877</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1091,19 +1071,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4mk22</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1115,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>317</v>
+        <v>121</v>
       </c>
       <c r="Q7" t="n">
-        <v>1930</v>
+        <v>178</v>
       </c>
       <c r="R7" t="n">
-        <v>2247</v>
+        <v>299</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1063156519</t>
+          <t>1650465158</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1063156519</t>
+          <t>https://m.place.naver.com/place/1650465158</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">

--- a/naver-place-crawler/results_health/인천_PT.xlsx
+++ b/naver-place-crawler/results_health/인천_PT.xlsx
@@ -421,18 +421,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>카우짐24시 서구청역점</t>
+          <t>그린짐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>coco951215@naver.com</t>
+          <t>green_gym@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1376-7926</t>
+          <t>0507-1482-4423</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 서구 탁옥로51번길 11 702호, 703호, 704호</t>
+          <t>인천광역시 부평구 부평북로 339 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/cowgymseogu</t>
+          <t>https://blog.naver.com/green_gym</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -612,22 +612,22 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1020</v>
+        <v>321</v>
       </c>
       <c r="Q2" t="n">
-        <v>324</v>
+        <v>822</v>
       </c>
       <c r="R2" t="n">
-        <v>1344</v>
+        <v>1143</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1106839652</t>
+          <t>1527477204</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1106839652</t>
+          <t>https://m.place.naver.com/place/1527477204</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,39 +653,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>아이언휘트니스 헬스&amp;PT 삼산점</t>
+          <t>바모스 필라테스 요가 PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ironfitnesssamsan@naver.com</t>
+          <t>vamos-pilates@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1483-2126</t>
+          <t>0507-1350-2275</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부평북로 448 로얄프라자 2층</t>
+          <t>인천 미추홀구 독배로 311 11층 1104호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ironfitnesssamsan</t>
+          <t>https://litt.ly/vamos_wellness_club</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,18 +695,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wba8f8p</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>710</v>
+        <v>47</v>
       </c>
       <c r="Q3" t="n">
-        <v>291</v>
+        <v>64</v>
       </c>
       <c r="R3" t="n">
-        <v>1001</v>
+        <v>111</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1098353648</t>
+          <t>1769749787</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1098353648</t>
+          <t>https://m.place.naver.com/place/1769749787</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,39 +751,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>커넥트짐 구월동 헬스&amp;PT</t>
+          <t>카우짐24시 서구청역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>connectgympro@naver.com</t>
+          <t>coco951215@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1382-1877</t>
+          <t>0507-1376-7926</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인주대로 593 엔타스빌딩 1층 커넥트짐 구월점</t>
+          <t>인천광역시 서구 탁옥로51번길 11 702호, 703호, 704호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/connectgym.pro</t>
+          <t>https://link.inpock.co.kr/cowgymseogu</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -789,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -800,22 +804,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>658</v>
+        <v>1020</v>
       </c>
       <c r="Q4" t="n">
-        <v>870</v>
+        <v>324</v>
       </c>
       <c r="R4" t="n">
-        <v>1528</v>
+        <v>1344</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1964930363</t>
+          <t>1106839652</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1964930363</t>
+          <t>https://m.place.naver.com/place/1106839652</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>샤머니짐 송도점</t>
+          <t>커넥트짐 구월동 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>shamanigym_songdo@naver.com</t>
+          <t>connectgympro@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1330-9030</t>
+          <t>0507-1382-1877</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
+          <t>인천광역시 남동구 인주대로 593 엔타스빌딩 1층 커넥트짐 구월점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shamanigym/</t>
+          <t>https://www.instagram.com/connectgym.pro</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -894,7 +898,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1387</v>
+        <v>659</v>
       </c>
       <c r="Q5" t="n">
-        <v>933</v>
+        <v>874</v>
       </c>
       <c r="R5" t="n">
-        <v>2320</v>
+        <v>1533</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +922,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1040543457</t>
+          <t>1964930363</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040543457</t>
+          <t>https://m.place.naver.com/place/1964930363</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,34 +944,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>더피티짐 프리미엄 학원가점</t>
+          <t>샤머니짐 송도점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>qoqofh677@naver.com</t>
+          <t>shamanigym_songdo@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1446-9681</t>
+          <t>0507-1330-9030</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
+          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://theptgym.clickn.co.kr/</t>
+          <t>https://www.instagram.com/shamanigym/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -997,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>317</v>
+        <v>1387</v>
       </c>
       <c r="Q6" t="n">
-        <v>1932</v>
+        <v>935</v>
       </c>
       <c r="R6" t="n">
-        <v>2249</v>
+        <v>2322</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1063156519</t>
+          <t>1040543457</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1063156519</t>
+          <t>https://m.place.naver.com/place/1040543457</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,34 +1038,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>더피티짐 프리미엄 루원시티점</t>
+          <t>더피티짐 프리미엄 학원가점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gktk1877@naver.com</t>
+          <t>qoqofh677@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1375-9681</t>
+          <t>0507-1446-9681</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오대로 270 302동 상가B 110~112호 (파리바게트 위층)</t>
+          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gktk1877</t>
+          <t>https://theptgym.clickn.co.kr/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1071,7 +1075,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>121</v>
+        <v>317</v>
       </c>
       <c r="Q7" t="n">
-        <v>178</v>
+        <v>1934</v>
       </c>
       <c r="R7" t="n">
-        <v>299</v>
+        <v>2251</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1650465158</t>
+          <t>1063156519</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1650465158</t>
+          <t>https://m.place.naver.com/place/1063156519</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">

--- a/naver-place-crawler/results_health/인천_PT.xlsx
+++ b/naver-place-crawler/results_health/인천_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>바모스 필라테스 요가 PT</t>
+          <t>그린짐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>vamos-pilates@naver.com</t>
+          <t>green_gym@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1350-2275</t>
+          <t>0507-1482-4423</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 미추홀구 독배로 311 11층 1104호</t>
+          <t>인천 부평구 부평북로 339 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://litt.ly/vamos_wellness_club</t>
+          <t>https://blog.naver.com/green_gym</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wba8f8p</t>
+          <t>https://talk.naver.com/ct/w4fs9p</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>47</v>
+        <v>321</v>
       </c>
       <c r="Q2" t="n">
-        <v>64</v>
+        <v>822</v>
       </c>
       <c r="R2" t="n">
-        <v>111</v>
+        <v>1143</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1769749787</t>
+          <t>1527477204</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1769749787</t>
+          <t>https://m.place.naver.com/place/1527477204</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>카우짐24시 서구청역점</t>
+          <t>바모스 필라테스 요가 PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>coco951215@naver.com</t>
+          <t>vamos-pilates@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1376-7926</t>
+          <t>0507-1350-2275</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 서구 탁옥로51번길 11 702호, 703호, 704호</t>
+          <t>인천 미추홀구 독배로 311 11층 1104호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/cowgymseogu</t>
+          <t>https://litt.ly/vamos_wellness_club</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,15 +699,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wba8f8p</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,17 +719,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1020</v>
+        <v>47</v>
       </c>
       <c r="Q3" t="n">
-        <v>324</v>
+        <v>64</v>
       </c>
       <c r="R3" t="n">
-        <v>1344</v>
+        <v>111</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1106839652</t>
+          <t>1769749787</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1106839652</t>
+          <t>https://m.place.naver.com/place/1769749787</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -751,39 +755,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>커넥트짐 구월동 헬스&amp;PT</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>connectgympro@naver.com</t>
-        </is>
-      </c>
+          <t>카우짐24시 서구청역점</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1382-1877</t>
+          <t>0507-1376-7926</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인주대로 593 엔타스빌딩 1층 커넥트짐 구월점</t>
+          <t>인천 서구 탁옥로51번길 11 702호, 703호, 704호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/connectgym.pro</t>
+          <t>https://link.inpock.co.kr/cowgymseogu</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -793,33 +793,37 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5xn31</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>660</v>
+        <v>1020</v>
       </c>
       <c r="Q4" t="n">
-        <v>882</v>
+        <v>324</v>
       </c>
       <c r="R4" t="n">
-        <v>1542</v>
+        <v>1344</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1964930363</t>
+          <t>1106839652</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1964930363</t>
+          <t>https://m.place.naver.com/place/1106839652</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -850,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>샤머니짐 송도점</t>
+          <t>커넥트짐 구월동 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>shamanigym_songdo@naver.com</t>
+          <t>connectgympro@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1330-9030</t>
+          <t>0507-1382-1877</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
+          <t>인천 남동구 인주대로 593 엔타스빌딩 1층 커넥트짐 구월점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shamanigym/</t>
+          <t>https://www.instagram.com/connectgym.pro</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -892,13 +896,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wz5kx6y</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -907,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1387</v>
+        <v>660</v>
       </c>
       <c r="Q5" t="n">
-        <v>937</v>
+        <v>884</v>
       </c>
       <c r="R5" t="n">
-        <v>2324</v>
+        <v>1544</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1040543457</t>
+          <t>1964930363</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040543457</t>
+          <t>https://m.place.naver.com/place/1964930363</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -944,34 +952,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>더피티짐 프리미엄 학원가점</t>
+          <t>샤머니짐 송도점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>qoqofh677@naver.com</t>
+          <t>shamanigym_songdo@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1446-9681</t>
+          <t>0507-1330-9030</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
+          <t>인천 연수구 컨벤시아대로 81 드림시티 7층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://theptgym.clickn.co.kr/</t>
+          <t>https://www.instagram.com/shamanigym/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -986,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7ng6u3</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1001,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>317</v>
+        <v>1387</v>
       </c>
       <c r="Q6" t="n">
-        <v>1938</v>
+        <v>937</v>
       </c>
       <c r="R6" t="n">
-        <v>2255</v>
+        <v>2324</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1063156519</t>
+          <t>1040543457</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1063156519</t>
+          <t>https://m.place.naver.com/place/1040543457</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1031,30 +1043,46 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>더피티짐 프리미엄 학원가점</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>qoqofh677@naver.com</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1446-9681</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>인천 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://theptgym.clickn.co.kr/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1064,10 +1092,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4mk22</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1075,17 +1107,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>317</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1938</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2255</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1094,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>7043481</t>
+          <t>1063156519</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7043481</t>
+          <t>https://m.place.naver.com/place/1063156519</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1172,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>7279520</t>
+          <t>7043481</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7279520</t>
+          <t>https://m.place.naver.com/place/7043481</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,12 +1282,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7166733</t>
+          <t>7279520</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7166733</t>
+          <t>https://m.place.naver.com/place/7279520</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1328,12 +1360,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>7226084</t>
+          <t>7166733</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7226084</t>
+          <t>https://m.place.naver.com/place/7166733</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1406,15 +1438,93 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>7226084</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7226084</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>7484708</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/7484708</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
